--- a/CodeAlpha_Restaurant_Sales_Analysis.xlsx
+++ b/CodeAlpha_Restaurant_Sales_Analysis.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Projects Portfolio\CodeAlpha_Data_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E6BDA3F-A23D-413E-A59F-FA00B1E8BA3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB4493E-1E19-4CA8-A4E3-C193EC319F65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="1" xr2:uid="{66301FCA-EA2A-4B3B-9A5C-535C597A10AA}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5039" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="1056">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -3288,10 +3288,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3635,167 +3635,119 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$4:$A$29</c:f>
+              <c:f>Sheet1!$A$4:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>Apple Pie</c:v>
+                  <c:v>BBQ Ribs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>BBQ Ribs</c:v>
+                  <c:v>Bruschetta</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Bruschetta</c:v>
+                  <c:v>Buffalo Wings</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Buffalo Wings</c:v>
+                  <c:v>Caesar Salad</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Burger Deluxe</c:v>
+                  <c:v>Cheesecake</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Caesar Salad</c:v>
+                  <c:v>Chicken Parmesan</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Cheesecake</c:v>
+                  <c:v>Craft Beer</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Chicken Parmesan</c:v>
+                  <c:v>Fish &amp; Chips</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Chocolate Lava Cake</c:v>
+                  <c:v>Fresh Lemonade</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Craft Beer</c:v>
+                  <c:v>Grilled Salmon</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Fish &amp; Chips</c:v>
+                  <c:v>Iced Coffee</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Fresh Lemonade</c:v>
+                  <c:v>Mushroom Risotto</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Grilled Salmon</c:v>
+                  <c:v>Pasta Primavera</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>House Wine</c:v>
+                  <c:v>Smoothie</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Ice Cream Sundae</c:v>
+                  <c:v>Soup of the Day</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Iced Coffee</c:v>
+                  <c:v>Sparkling Water</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>Mozzarella Sticks</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Mushroom Risotto</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>NY Strip Steak</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Pasta Primavera</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Smoothie</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Soup of the Day</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Sparkling Water</c:v>
-                </c:pt>
-                <c:pt idx="23">
                   <c:v>Spring Rolls</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Tiramisu</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$29</c:f>
+              <c:f>Sheet1!$B$4:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>68.97</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.99</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.97</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107.94</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.99</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>199.92</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>84.949999999999989</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74.95</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20.97</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>8.99</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>137.94</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>71.94</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>164.89</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>287.82000000000005</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>64.95</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>142.87</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>208.89</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11.99</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>95.88000000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>233.86999999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.96</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>374.85</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>39.96</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>23.97</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>53.91</c:v>
+                  <c:v>17.450000000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>142.87</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>169.9</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>197.94000000000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>89.94</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>27.96</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>26.97</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>24.43</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>49.95</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>39.96</c:v>
+                  <c:v>29.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4605,19 +4557,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Order Type">
@@ -4640,7 +4592,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4650,8 +4602,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8791575" y="923925"/>
-              <a:ext cx="1828800" cy="2524125"/>
+              <a:off x="8343900" y="866775"/>
+              <a:ext cx="1828800" cy="3095625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4683,19 +4635,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Restaurant Location">
@@ -4718,7 +4670,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4728,8 +4680,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10648950" y="923925"/>
-              <a:ext cx="1828800" cy="2524125"/>
+              <a:off x="10401300" y="857250"/>
+              <a:ext cx="1828800" cy="3076575"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -16854,20 +16806,20 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D7E6DDB-C1CD-4AF9-9CF5-3E56BDE10645}" name="PivotTable15" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="A3:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D7E6DDB-C1CD-4AF9-9CF5-3E56BDE10645}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0">
       <items count="11">
         <item h="1" x="9"/>
-        <item x="4"/>
+        <item h="1" x="4"/>
         <item h="1" x="8"/>
         <item h="1" x="1"/>
         <item h="1" x="0"/>
         <item h="1" x="5"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item h="1" x="6"/>
         <item h="1" x="2"/>
         <item h="1" x="7"/>
@@ -16877,8 +16829,8 @@
     <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16921,10 +16873,7 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="26">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="18">
     <i>
       <x v="1"/>
     </i>
@@ -16935,9 +16884,6 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
-    </i>
-    <i>
       <x v="5"/>
     </i>
     <i>
@@ -16945,9 +16891,6 @@
     </i>
     <i>
       <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
     </i>
     <i>
       <x v="9"/>
@@ -16962,22 +16905,10 @@
       <x v="12"/>
     </i>
     <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
       <x v="15"/>
     </i>
     <i>
-      <x v="16"/>
-    </i>
-    <i>
       <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
     </i>
     <i>
       <x v="19"/>
@@ -16993,9 +16924,6 @@
     </i>
     <i>
       <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
     </i>
     <i t="grand">
       <x/>
@@ -17048,8 +16976,8 @@
     <tabular pivotCacheId="920242587">
       <items count="3">
         <i x="0" s="1"/>
-        <i x="2" s="1"/>
-        <i x="1" s="1"/>
+        <i x="2"/>
+        <i x="1"/>
       </items>
     </tabular>
   </data>
@@ -17065,12 +16993,12 @@
     <tabular pivotCacheId="920242587">
       <items count="10">
         <i x="9"/>
-        <i x="4" s="1"/>
+        <i x="4"/>
         <i x="8"/>
         <i x="1"/>
         <i x="0"/>
         <i x="5"/>
-        <i x="3"/>
+        <i x="3" s="1"/>
         <i x="6"/>
         <i x="2"/>
         <i x="7"/>
@@ -17404,10 +17332,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9F40B2-1283-4ECB-8789-A4B58205F4D4}">
-  <dimension ref="A3:B29"/>
+  <dimension ref="A3:B21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17421,210 +17349,146 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B4" s="6">
-        <v>8.99</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B5" s="6">
-        <v>137.94</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="B6" s="6">
-        <v>71.94</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="B7" s="6">
-        <v>164.89</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B8" s="6">
-        <v>287.82000000000005</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>64.95</v>
+        <v>37.979999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6">
-        <v>142.87</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="B11" s="6">
-        <v>208.89</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="B12" s="6">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6">
-        <v>95.88000000000001</v>
+        <v>199.92</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B14" s="6">
-        <v>233.86999999999998</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6">
-        <v>19.96</v>
+        <v>84.949999999999989</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B16" s="6">
-        <v>374.85</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6">
-        <v>39.96</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>23.97</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="B19" s="6">
-        <v>53.91</v>
+        <v>17.450000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B20" s="6">
-        <v>142.87</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>1054</v>
       </c>
       <c r="B21" s="6">
-        <v>169.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="6">
-        <v>197.94000000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="6">
-        <v>89.94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="6">
-        <v>27.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6">
-        <v>26.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6">
-        <v>24.43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="6">
-        <v>49.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" s="6">
-        <v>39.96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="5" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B29" s="6">
-        <v>2712.6</v>
+        <v>791.95000000000027</v>
       </c>
     </row>
   </sheetData>
@@ -17641,26 +17505,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18" ht="27.75">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
